--- a/ig/TEST-SUPPLEMENT/CodeSystem-TRE-R21-Fonction.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-TRE-R21-Fonction.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="170">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20251023120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-10-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>54</t>
+    <t>55</t>
   </si>
   <si>
     <t>Code</t>
@@ -512,6 +512,12 @@
   </si>
   <si>
     <t>Pharmacien remplaçant BPDO</t>
+  </si>
+  <si>
+    <t>FON-62</t>
+  </si>
+  <si>
+    <t>Consultations de solidarité territoriale</t>
   </si>
   <si>
     <t>FON-AU</t>
@@ -927,7 +933,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1596,6 +1602,18 @@
       </c>
       <c r="D55" s="2"/>
     </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
